--- a/healthcare_forms/039_event_medical_cover_enquiry_form--healthcare_forms.xlsx
+++ b/healthcare_forms/039_event_medical_cover_enquiry_form--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -780,8 +780,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -843,12 +843,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'basic',_'value':_'basic'}</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Basic', 'value': 'basic'}</t>
+          <t>Basic</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'comprehensive',_'value':_'comprehensive'}</t>
+          <t>comprehensive</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Comprehensive', 'value': 'comprehensive'}</t>
+          <t>Comprehensive</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'enhanced',_'value':_'enhanced'}</t>
+          <t>enhanced</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Enhanced', 'value': 'enhanced'}</t>
+          <t>Enhanced</t>
         </is>
       </c>
     </row>
@@ -894,12 +894,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'general',_'value':_'general'}</t>
+          <t>general</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'General', 'value': 'general'}</t>
+          <t>General</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'specific',_'value':_'specific'}</t>
+          <t>specific</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Specific', 'value': 'specific'}</t>
+          <t>Specific</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'new',_'value':_'new'}</t>
+          <t>new</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'New', 'value': 'new'}</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'in-progress',_'value':_'in_progress'}</t>
+          <t>in-progress</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'In-progress', 'value': 'in_progress'}</t>
+          <t>In-progress</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'completed',_'value':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Completed', 'value': 'completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
